--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>0.589</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.655</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.062</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.099</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.063</t>
         </is>
       </c>
     </row>

--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.636</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.120</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>

--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>0.728</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.596</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.655</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.123</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>0.014</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.007</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>

--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.636</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.120</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>

--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.601</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.639</t>
         </is>
       </c>
     </row>

--- a/tables/combined_metrics.xlsx
+++ b/tables/combined_metrics.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Methode</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
